--- a/output/full_scan/batch_seq1_2026-08-05.xlsx
+++ b/output/full_scan/batch_seq1_2026-08-05.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O132"/>
+  <dimension ref="A1:O133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1693,21 +1693,21 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1216</v>
+        <v>1515</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>400.5992804174006</v>
+        <v>405.7859096423141</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>73.2</v>
+        <v>30.9</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>36.66647678026376</v>
+        <v>45.5515076213078</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>25.36608236727419</v>
+        <v>33.58894662345204</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.7595356552963296</v>
+        <v>0.2050010668563772</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.7215253541363373</v>
+        <v>-1.331374448072231</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1513</v>
+        <v>1216</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>396.0635158083493</v>
+        <v>400.5992804174006</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>161</v>
+        <v>73.2</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>49.06797106027559</v>
+        <v>36.66647678026376</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>23.78363459159147</v>
+        <v>25.36608236727419</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.6543543121151149</v>
+        <v>0.7595356552963296</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.1871891755416035</v>
+        <v>-0.7215253541363373</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1526</v>
+        <v>1513</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>392.0963114931951</v>
+        <v>396.0635158083493</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>17.45</v>
+        <v>161</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>57.01100001945341</v>
+        <v>49.06797106027559</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>44.54471893051444</v>
+        <v>23.78363459159147</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4023459159641476</v>
+        <v>0.6543543121151149</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.0754339289765172</v>
+        <v>0.1871891755416035</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1459</v>
+        <v>1526</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>390.3676658645433</v>
+        <v>392.0963114931951</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>12.9</v>
+        <v>17.45</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>73.10295612322037</v>
+        <v>57.01100001945341</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>19.61956153134032</v>
+        <v>44.54471893051444</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.397906986842677</v>
+        <v>0.4023459159641476</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1335704074752651</v>
+        <v>0.0754339289765172</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1315</v>
+        <v>1459</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>382.3819087107354</v>
+        <v>390.3676658645433</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>63.3</v>
+        <v>12.9</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>48.45737851597275</v>
+        <v>73.10295612322037</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>23.24999780696924</v>
+        <v>19.61956153134032</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.236462534966694</v>
+        <v>1.397906986842677</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.1556117501137404</v>
+        <v>0.1335704074752651</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1568</v>
+        <v>1315</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>380.8763159326516</v>
+        <v>382.3819087107354</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>28.4</v>
+        <v>63.3</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>39.54271058275597</v>
+        <v>48.45737851597275</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>25.57104820593008</v>
+        <v>23.24999780696924</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.6106380236423049</v>
+        <v>1.236462534966694</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.1411358629035199</v>
+        <v>-0.1556117501137404</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1470</v>
+        <v>1568</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>375.6295069172119</v>
+        <v>380.8763159326516</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>22.9</v>
+        <v>28.4</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>52.66453030204436</v>
+        <v>39.54271058275597</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>6.086789462136953</v>
+        <v>25.57104820593008</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5534880074523965</v>
+        <v>0.6106380236423049</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.07800194206639161</v>
+        <v>0.1411358629035199</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1418</v>
+        <v>1470</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>373.1540031742055</v>
+        <v>375.6295069172119</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>18.3</v>
+        <v>22.9</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>48.98899416002275</v>
+        <v>52.66453030204436</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>22.25245145884362</v>
+        <v>6.086789462136953</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.3629419407347434</v>
+        <v>0.5534880074523965</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.0515108503851601</v>
+        <v>-0.07800194206639161</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1439</v>
+        <v>1418</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>371.8559866859415</v>
+        <v>373.1540031742055</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>29.1</v>
+        <v>18.3</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>71.52980753269505</v>
+        <v>48.98899416002275</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>15.58093268366519</v>
+        <v>22.25245145884362</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.785598668594143</v>
+        <v>0.3629419407347434</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.2897372352309929</v>
+        <v>-0.0515108503851601</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>367.2023935756925</v>
+        <v>371.8559866859415</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>29.5</v>
+        <v>29.1</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>55.20074828598581</v>
+        <v>71.52980753269505</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>24.73617308489598</v>
+        <v>15.58093268366519</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4381017812197947</v>
+        <v>0.785598668594143</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.1294222690999451</v>
+        <v>0.2897372352309929</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>363.8351474545719</v>
+        <v>367.2023935756925</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>6.93</v>
+        <v>29.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>43.15422959708973</v>
+        <v>55.20074828598581</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>22.11894929075466</v>
+        <v>24.73617308489598</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.180603957536028</v>
+        <v>0.4381017812197947</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.1657709450866087</v>
+        <v>-0.1294222690999451</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1307</v>
+        <v>1447</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>360.7116859961026</v>
+        <v>363.8351474545719</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>32</v>
+        <v>6.93</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>47.06510787741691</v>
+        <v>43.15422959708973</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>20.35768145179697</v>
+        <v>22.11894929075466</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.4742754579986492</v>
+        <v>1.180603957536028</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.052426854143471</v>
+        <v>-0.1657709450866087</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1101</v>
+        <v>1307</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>354.3281441731229</v>
+        <v>360.7116859961026</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>24.05</v>
+        <v>32</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>51.41237155464896</v>
+        <v>47.06510787741691</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>17.96360288651185</v>
+        <v>20.35768145179697</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.6976841178204227</v>
+        <v>0.4742754579986492</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0142436236253316</v>
+        <v>0.052426854143471</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>350.6932960481681</v>
+        <v>354.3281441731229</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>32.6</v>
+        <v>24.05</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>38.4268459838456</v>
+        <v>51.41237155464896</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>30.1722204250716</v>
+        <v>17.96360288651185</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4977427988661861</v>
+        <v>0.6976841178204227</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.0356136957435617</v>
+        <v>0.0142436236253316</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1413</v>
+        <v>1102</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>350.6335238697717</v>
+        <v>350.6932960481681</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>43.85094277084569</v>
+        <v>38.4268459838456</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>20.60486986164892</v>
+        <v>30.1722204250716</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3450030554192163</v>
+        <v>0.4977427988661861</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.0641952919603265</v>
+        <v>-0.0356136957435617</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1314</v>
+        <v>1413</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>348.2270119133201</v>
+        <v>350.6335238697717</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>7.84</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>44.30057642288752</v>
+        <v>43.85094277084569</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>20.5020367512515</v>
+        <v>20.60486986164892</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.7360966002268921</v>
+        <v>0.3450030554192163</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.1046569840483024</v>
+        <v>-0.0641952919603265</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1563</v>
+        <v>1314</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>347.5166752244333</v>
+        <v>348.2270119133201</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>56.4</v>
+        <v>7.84</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>42.83199184232375</v>
+        <v>44.30057642288752</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>20.04395688292458</v>
+        <v>20.5020367512515</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.4739304000320606</v>
+        <v>0.7360966002268921</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.7012392819561022</v>
+        <v>-0.1046569840483024</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1319</v>
+        <v>1563</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>346.3295693466297</v>
+        <v>347.5166752244333</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>42.10171791704914</v>
+        <v>42.83199184232375</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>34.02862013382663</v>
+        <v>20.04395688292458</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.594056750727064</v>
+        <v>0.4739304000320606</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.4869860711581464</v>
+        <v>-0.7012392819561022</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1437</v>
+        <v>1319</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>345.8295397467828</v>
+        <v>346.3295693466297</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>29.75</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>37.25501143288567</v>
+        <v>42.10171791704914</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>19.97862665099463</v>
+        <v>34.02862013382663</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.008928026451664</v>
+        <v>0.594056750727064</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.1316865400417413</v>
+        <v>0.4869860711581464</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1528</v>
+        <v>1437</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>335.1154516192909</v>
+        <v>345.8295397467828</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>18.4</v>
+        <v>29.75</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>36.52937164777438</v>
+        <v>37.25501143288567</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>44.17763766725568</v>
+        <v>19.97862665099463</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.7327834582913169</v>
+        <v>1.008928026451664</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0270460802841483</v>
+        <v>-0.1316865400417413</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1569</v>
+        <v>1528</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>332.1558653183251</v>
+        <v>335.1154516192909</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>42.65</v>
+        <v>18.4</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>46.90796450033718</v>
+        <v>36.52937164777438</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>26.10957371002879</v>
+        <v>44.17763766725568</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.7231646316769977</v>
+        <v>0.7327834582913169</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1454104301977823</v>
+        <v>0.0270460802841483</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending, dealer_buy_3d</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1342</v>
+        <v>1569</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>331.1907058029352</v>
+        <v>332.1558653183251</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>102</v>
+        <v>42.65</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>40.6177795277567</v>
+        <v>46.90796450033718</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>30.44070465062533</v>
+        <v>26.10957371002879</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.6501625621549737</v>
+        <v>0.7231646316769977</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-1.554433956779912</v>
+        <v>0.1454104301977823</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1225</v>
+        <v>1342</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>330.8237183719884</v>
+        <v>331.1907058029352</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>24.25</v>
+        <v>102</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>27.26055239422692</v>
+        <v>40.6177795277567</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>31.17820312524091</v>
+        <v>30.44070465062533</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.6303080294729088</v>
+        <v>0.6501625621549737</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.1845317590055736</v>
+        <v>-1.554433956779912</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1506</v>
+        <v>1225</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>322.8665610746861</v>
+        <v>330.8237183719884</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>10.3</v>
+        <v>24.25</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>45.44676264108426</v>
+        <v>27.26055239422692</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>27.54088873440362</v>
+        <v>31.17820312524091</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4375500166021798</v>
+        <v>0.6303080294729088</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.0622800157383748</v>
+        <v>-0.1845317590055736</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1256</v>
+        <v>1506</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>320.9560943164981</v>
+        <v>322.8665610746861</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>186</v>
+        <v>10.3</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>52.27979441207463</v>
+        <v>45.44676264108426</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>13.98330165000392</v>
+        <v>27.54088873440362</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>3.060493842471445</v>
+        <v>0.4375500166021798</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0905017869846523</v>
+        <v>-0.0622800157383748</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1339</v>
+        <v>1256</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>320.7846357260353</v>
+        <v>320.9560943164981</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>44.45</v>
+        <v>186</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>52.4439657408419</v>
+        <v>52.27979441207463</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>14.60395443818113</v>
+        <v>13.98330165000392</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.8789987768464018</v>
+        <v>3.060493842471445</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.0523045122952592</v>
+        <v>-0.0905017869846523</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1313</v>
+        <v>1339</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>316.9730045459817</v>
+        <v>320.7846357260353</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>11</v>
+        <v>44.45</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>43.5110395302607</v>
+        <v>52.4439657408419</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>22.947249984366</v>
+        <v>14.60395443818113</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.5969441832775892</v>
+        <v>0.8789987768464018</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.154293393615769</v>
+        <v>-0.0523045122952592</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1504</v>
+        <v>1313</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>316.6797308544308</v>
+        <v>316.9730045459817</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>66.5</v>
+        <v>11</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>49.17432900630043</v>
+        <v>43.5110395302607</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>13.36797535155202</v>
+        <v>22.947249984366</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6538428017183665</v>
+        <v>0.5969441832775892</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.1298116273953145</v>
+        <v>-0.154293393615769</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1471</v>
+        <v>1504</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>315.7193111554777</v>
+        <v>316.6797308544308</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>9.5</v>
+        <v>66.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>38.5346494113077</v>
+        <v>49.17432900630043</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>28.06671281537197</v>
+        <v>13.36797535155202</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.188346177461357</v>
+        <v>0.6538428017183665</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0006895864657787</v>
+        <v>0.1298116273953145</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1419</v>
+        <v>1471</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>314.4907881516054</v>
+        <v>315.7193111554777</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>65.59999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>44.85675301390604</v>
+        <v>38.5346494113077</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>20.23885504766118</v>
+        <v>28.06671281537197</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.077453689550059</v>
+        <v>1.188346177461357</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.1789629711202846</v>
+        <v>0.0006895864657787</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1527</v>
+        <v>1419</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>313.8996800386493</v>
+        <v>314.4907881516054</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>32.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>37.61532469633138</v>
+        <v>44.85675301390604</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>20.30083095254156</v>
+        <v>20.23885504766118</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4642521888639397</v>
+        <v>1.077453689550059</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.1728315350261049</v>
+        <v>-0.1789629711202846</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1516</v>
+        <v>1527</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>312.7111152759596</v>
+        <v>313.8996800386493</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>15.8</v>
+        <v>32.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>36.12464890584501</v>
+        <v>37.61532469633138</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>57.94224072853708</v>
+        <v>20.30083095254156</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.1510111429822115</v>
+        <v>0.4642521888639397</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.1087772848174188</v>
+        <v>-0.1728315350261049</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1444</v>
+        <v>1516</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>308.1567005638207</v>
+        <v>312.7111152759596</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>7.16</v>
+        <v>15.8</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>39.63181814952516</v>
+        <v>36.12464890584501</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21.30523436597618</v>
+        <v>57.94224072853708</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.4674685885363149</v>
+        <v>0.1510111429822115</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.1459057099955064</v>
+        <v>0.1087772848174188</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1416</v>
+        <v>1444</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>305.1130267154998</v>
+        <v>308.1567005638207</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>10.85</v>
+        <v>7.16</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>45.06471199380528</v>
+        <v>39.63181814952516</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>25.15743138305037</v>
+        <v>21.30523436597618</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.089442655166767</v>
+        <v>0.4674685885363149</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.0147268788733147</v>
+        <v>-0.1459057099955064</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1312</v>
+        <v>1416</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>303.0009346258533</v>
+        <v>305.1130267154998</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>12.1</v>
+        <v>10.85</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>45.22717835213563</v>
+        <v>45.06471199380528</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>18.49967032617815</v>
+        <v>25.15743138305037</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.4593947183414469</v>
+        <v>1.089442655166767</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.1314568983820424</v>
+        <v>-0.0147268788733147</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1215</v>
+        <v>1312</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>301.7496831434473</v>
+        <v>303.0009346258533</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>104</v>
+        <v>12.1</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>31.26075028690748</v>
+        <v>45.22717835213563</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>52.70972049714258</v>
+        <v>18.49967032617815</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5165535124380476</v>
+        <v>0.4593947183414469</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.1603800886566486</v>
+        <v>-0.1314568983820424</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1231</v>
+        <v>1215</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>300.2752313819547</v>
+        <v>301.7496831434473</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>80.09999999999999</v>
+        <v>104</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>29.81016966790277</v>
+        <v>31.26075028690748</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>25.89198311041349</v>
+        <v>52.70972049714258</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.9275231381954646</v>
+        <v>0.5165535124380476</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-1.34761615108984</v>
+        <v>-0.1603800886566486</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3654,21 +3654,21 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1456</v>
+        <v>1231</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>297.4550836597421</v>
+        <v>300.2752313819547</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>14.1</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>52.52851461422416</v>
+        <v>29.81016966790277</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>9.922477395114717</v>
+        <v>25.89198311041349</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.4665314793480871</v>
+        <v>0.9275231381954646</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0374270762510701</v>
+        <v>-1.34761615108984</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1227</v>
+        <v>1456</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>296.7341475175479</v>
+        <v>297.4550836597421</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>28.7</v>
+        <v>14.1</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>40.6586979614212</v>
+        <v>52.52851461422416</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>18.47295015630107</v>
+        <v>9.922477395114717</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5547128191742748</v>
+        <v>0.4665314793480871</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.1494185119739877</v>
+        <v>0.0374270762510701</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1514</v>
+        <v>1227</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>293.1994953935862</v>
+        <v>296.7341475175479</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>101.5</v>
+        <v>28.7</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>41.41559285237597</v>
+        <v>40.6586979614212</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>25.53016898992064</v>
+        <v>18.47295015630107</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3484780066373284</v>
+        <v>0.5547128191742748</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.1576979205949769</v>
+        <v>-0.1494185119739877</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1558</v>
+        <v>1514</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>290.8069476742565</v>
+        <v>293.1994953935862</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>91</v>
+        <v>101.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>47.0755765080812</v>
+        <v>41.41559285237597</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>19.39024575562985</v>
+        <v>25.53016898992064</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5433899291471362</v>
+        <v>0.3484780066373284</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.111847744040622</v>
+        <v>-0.1576979205949769</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1533</v>
+        <v>1558</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>290.8021780746155</v>
+        <v>290.8069476742565</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>32.6</v>
+        <v>91</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>41.16047073625195</v>
+        <v>47.0755765080812</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>31.817079759157</v>
+        <v>19.39024575562985</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.6419664080726381</v>
+        <v>0.5433899291471362</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.0314704442841231</v>
+        <v>-0.111847744040622</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1432</v>
+        <v>1533</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>284.4816726311274</v>
+        <v>290.8021780746155</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>15.1</v>
+        <v>32.6</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>41.01574047252994</v>
+        <v>41.16047073625195</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>31.05247106757146</v>
+        <v>31.817079759157</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.6888522138867607</v>
+        <v>0.6419664080726381</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.06362410562835299</v>
+        <v>-0.0314704442841231</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1503</v>
+        <v>1432</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>283.8079010769989</v>
+        <v>284.4816726311274</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>197.5</v>
+        <v>15.1</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>42.76325804903141</v>
+        <v>41.01574047252994</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>27.54520020001754</v>
+        <v>31.05247106757146</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6228023399641746</v>
+        <v>0.6888522138867607</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.3092299747248166</v>
+        <v>0.06362410562835299</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1218</v>
+        <v>1503</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>283.0012851119233</v>
+        <v>283.8079010769989</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>15.5</v>
+        <v>197.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>33.69581176405759</v>
+        <v>42.76325804903141</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>41.51011425523572</v>
+        <v>27.54520020001754</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.049739552956647</v>
+        <v>0.6228023399641746</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.0019106402715051</v>
+        <v>-0.3092299747248166</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1538</v>
+        <v>1218</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>278.5284097908702</v>
+        <v>283.0012851119233</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>41.29875941499822</v>
+        <v>33.69581176405759</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>8.841798618029912</v>
+        <v>41.51011425523572</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.0185662526812913</v>
+        <v>1.049739552956647</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.9772817505565828</v>
+        <v>-0.0019106402715051</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1409</v>
+        <v>1538</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>274.859195162736</v>
+        <v>278.5284097908702</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>22.6</v>
+        <v>0</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>44.66219942104759</v>
+        <v>41.29875941499822</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>21.69800674185388</v>
+        <v>8.841798618029912</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.375901223706899</v>
+        <v>0.0185662526812913</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.1976362922487006</v>
+        <v>-0.9772817505565828</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1220</v>
+        <v>1409</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>274.1822310213383</v>
+        <v>274.859195162736</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>11.15</v>
+        <v>22.6</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>33.45802894400886</v>
+        <v>44.66219942104759</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>35.60277747670068</v>
+        <v>21.69800674185388</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.115423995365865</v>
+        <v>0.375901223706899</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.0027313381140434</v>
+        <v>-0.1976362922487006</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1321</v>
+        <v>1220</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>270.0086963453722</v>
+        <v>274.1822310213383</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>31.6</v>
+        <v>11.15</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>48.45202836345017</v>
+        <v>33.45802894400886</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>17.10380502755784</v>
+        <v>35.60277747670068</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5078346932794551</v>
+        <v>1.115423995365865</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.0958582916962011</v>
+        <v>-0.0027313381140434</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1438</v>
+        <v>1321</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>269.7173672217151</v>
+        <v>270.0086963453722</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>22.55</v>
+        <v>31.6</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>53.44791231106772</v>
+        <v>48.45202836345017</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>17.2479072299777</v>
+        <v>17.10380502755784</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.2857910224866064</v>
+        <v>0.5078346932794551</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.1054231881412703</v>
+        <v>-0.0958582916962011</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1341</v>
+        <v>1438</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>269.3221977371786</v>
+        <v>269.7173672217151</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>59.4</v>
+        <v>22.55</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>52.06869974323772</v>
+        <v>53.44791231106772</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>8.258225391796282</v>
+        <v>17.2479072299777</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.198433317587782</v>
+        <v>0.2857910224866064</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.4214940240134428</v>
+        <v>0.1054231881412703</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1532</v>
+        <v>1341</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>261.9910055396571</v>
+        <v>269.3221977371786</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>21.65</v>
+        <v>59.4</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>37.02540330308393</v>
+        <v>52.06869974323772</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>26.50306605972641</v>
+        <v>8.258225391796282</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4637721201585185</v>
+        <v>1.198433317587782</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.2052308500852385</v>
+        <v>0.4214940240134428</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1443</v>
+        <v>1532</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>255.3206216912967</v>
+        <v>261.9910055396571</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>25.75</v>
+        <v>21.65</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>44.40806305307112</v>
+        <v>37.02540330308393</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>10.14019228495786</v>
+        <v>26.50306605972641</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.4781430149059724</v>
+        <v>0.4637721201585185</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0618345775242864</v>
+        <v>-0.2052308500852385</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1519</v>
+        <v>1443</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>251.7256292595257</v>
+        <v>255.3206216912967</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>663</v>
+        <v>25.75</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>39.52789477538649</v>
+        <v>44.40806305307112</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>28.30127786254842</v>
+        <v>10.14019228495786</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.01506957082458</v>
+        <v>0.4781430149059724</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>3.805575966772288</v>
+        <v>-0.0618345775242864</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1219</v>
+        <v>1519</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>251.5242315961572</v>
+        <v>251.7256292595257</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>10.6</v>
+        <v>663</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>19.53222572963858</v>
+        <v>39.52789477538649</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>32.04031102113936</v>
+        <v>28.30127786254842</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.189756344476554</v>
+        <v>1.01506957082458</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.1017321492100856</v>
+        <v>3.805575966772288</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1423</v>
+        <v>1219</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>249.6459129646681</v>
+        <v>251.5242315961572</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>35.5</v>
+        <v>10.6</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>33.62324282243374</v>
+        <v>19.53222572963858</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>16.54632329681522</v>
+        <v>32.04031102113936</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.1696630002360072</v>
+        <v>1.189756344476554</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.1039966703202082</v>
+        <v>-0.1017321492100856</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1213</v>
+        <v>1423</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>249.5127172300672</v>
+        <v>249.6459129646681</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>7.5</v>
+        <v>35.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>53.69831459248354</v>
+        <v>33.62324282243374</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>12.24484073059522</v>
+        <v>16.54632329681522</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.017653343282064</v>
+        <v>0.1696630002360072</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.4162305387310004</v>
+        <v>0.1039966703202082</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1536</v>
+        <v>1213</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>240.9203182080878</v>
+        <v>249.5127172300672</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>51.6</v>
+        <v>7.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>54.722079150894</v>
+        <v>53.69831459248354</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>13.39969422812901</v>
+        <v>12.24484073059522</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6904018271367862</v>
+        <v>1.017653343282064</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0039483713128965</v>
+        <v>0.4162305387310004</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, liquidity_ok, hist_turn_positive</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1402</v>
+        <v>1536</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>238.8752496808573</v>
+        <v>240.9203182080878</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>26.7</v>
+        <v>51.6</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>40.40441896295553</v>
+        <v>54.722079150894</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>15.67658653886204</v>
+        <v>13.39969422812901</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.9365489727275632</v>
+        <v>0.6904018271367862</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.0638666927832144</v>
+        <v>0.0039483713128965</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>macd_golden_cross, market_above_ma60, liquidity_ok, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1560</v>
+        <v>1402</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>238.6376453872097</v>
+        <v>238.8752496808573</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>680</v>
+        <v>26.7</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>50.72416041846675</v>
+        <v>40.40441896295553</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>14.78130188946382</v>
+        <v>15.67658653886204</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.7075582508758338</v>
+        <v>0.9365489727275632</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.1927943711340525</v>
+        <v>-0.0638666927832144</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1435</v>
+        <v>1560</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>237.7972685636783</v>
+        <v>238.6376453872097</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>23</v>
+        <v>680</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>50.83883452983279</v>
+        <v>50.72416041846675</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>9.17074127740093</v>
+        <v>14.78130188946382</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.261858773495904</v>
+        <v>0.7075582508758338</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.2409967014400241</v>
+        <v>-0.1927943711340525</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1537</v>
+        <v>1435</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>223.7865789766892</v>
+        <v>237.7972685636783</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>125.5</v>
+        <v>23</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>45.85978445898768</v>
+        <v>50.83883452983279</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>14.13166367864725</v>
+        <v>9.17074127740093</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.082936282095302</v>
+        <v>1.261858773495904</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.09169777412464621</v>
+        <v>-0.2409967014400241</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1522</v>
+        <v>1537</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>223.6743561953208</v>
+        <v>223.7865789766892</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>28.2</v>
+        <v>125.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>42.5499426950355</v>
+        <v>45.85978445898768</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>27.8020886221607</v>
+        <v>14.13166367864725</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.4607692073020049</v>
+        <v>1.082936282095302</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0474609910765035</v>
+        <v>-0.09169777412464621</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1217</v>
+        <v>1522</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>219.779146466529</v>
+        <v>223.6743561953208</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>9.83</v>
+        <v>28.2</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>42.38218545438769</v>
+        <v>42.5499426950355</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>13.54980805698216</v>
+        <v>27.8020886221607</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.9026320210152672</v>
+        <v>0.4607692073020049</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.024047609971002</v>
+        <v>0.0474609910765035</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1524</v>
+        <v>1217</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>218.9749447633546</v>
+        <v>219.779146466529</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>26.4</v>
+        <v>9.83</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>40.30999110276555</v>
+        <v>42.38218545438769</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>34.71973136490183</v>
+        <v>13.54980805698216</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5822641282279998</v>
+        <v>0.9026320210152672</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0948925216418382</v>
+        <v>-0.024047609971002</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1229</v>
+        <v>1524</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>218.6816776090387</v>
+        <v>218.9749447633546</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>40.1</v>
+        <v>26.4</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>42.64228535042417</v>
+        <v>40.30999110276555</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>11.69495148867534</v>
+        <v>34.71973136490183</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.5000938630885712</v>
+        <v>0.5822641282279998</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.093042625407947</v>
+        <v>0.0948925216418382</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1474</v>
+        <v>1229</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>216.7758217604362</v>
+        <v>218.6816776090387</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>40.1</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>38.11754906769596</v>
+        <v>42.64228535042417</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>20.45467182466601</v>
+        <v>11.69495148867534</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5814601860015843</v>
+        <v>0.5000938630885712</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.062539519831006</v>
+        <v>-0.093042625407947</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>216.3810514888968</v>
+        <v>216.7758217604362</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>26.85</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>47.4446037909856</v>
+        <v>38.11754906769596</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>10.53019899025876</v>
+        <v>20.45467182466601</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.085532868219723</v>
+        <v>0.5814601860015843</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.026143209357993</v>
+        <v>-0.062539519831006</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1309</v>
+        <v>1475</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>215.4967127890108</v>
+        <v>216.3810514888968</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>12.95</v>
+        <v>26.85</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>39.59962613504271</v>
+        <v>47.4446037909856</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>17.13230112777425</v>
+        <v>10.53019899025876</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4185877123898963</v>
+        <v>1.085532868219723</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.137844961379298</v>
+        <v>-0.026143209357993</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1530</v>
+        <v>1309</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>213.7755634787414</v>
+        <v>215.4967127890108</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>27.9</v>
+        <v>12.95</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>42.25273202444167</v>
+        <v>39.59962613504271</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>16.80182107846771</v>
+        <v>17.13230112777425</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.4126777731536233</v>
+        <v>0.4185877123898963</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.1974607373297367</v>
+        <v>-0.137844961379298</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1463</v>
+        <v>1530</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>213.298665702049</v>
+        <v>213.7755634787414</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>17.7</v>
+        <v>27.9</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>47.07018557996074</v>
+        <v>42.25273202444167</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>17.84839757934627</v>
+        <v>16.80182107846771</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.6841855518102296</v>
+        <v>0.4126777731536233</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0177944278863036</v>
+        <v>-0.1974607373297367</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1529</v>
+        <v>1463</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>207.5514371828813</v>
+        <v>213.298665702049</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>17.15</v>
+        <v>17.7</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>29.3726052605617</v>
+        <v>47.07018557996074</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>32.09858072315453</v>
+        <v>17.84839757934627</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.4658797041784955</v>
+        <v>0.6841855518102296</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.1271581499677916</v>
+        <v>-0.0177944278863036</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1466</v>
+        <v>1529</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>202.1284687348144</v>
+        <v>207.5514371828813</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>16.25</v>
+        <v>17.15</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>48.87714401522118</v>
+        <v>29.3726052605617</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>16.25446059789539</v>
+        <v>32.09858072315453</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.2691132814717538</v>
+        <v>0.4658797041784955</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.2397195710050484</v>
+        <v>-0.1271581499677916</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1460</v>
+        <v>1466</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>201.4828000716956</v>
+        <v>202.1284687348144</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>6.62</v>
+        <v>16.25</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>37.84194474750404</v>
+        <v>48.87714401522118</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>16.59852274968637</v>
+        <v>16.25446059789539</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5643646102535416</v>
+        <v>0.2691132814717538</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.032086691778714</v>
+        <v>-0.2397195710050484</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1338</v>
+        <v>1460</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>194.1956074803861</v>
+        <v>201.4828000716956</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>15.45</v>
+        <v>6.62</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>38.53294382245742</v>
+        <v>37.84194474750404</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>32.69560096168198</v>
+        <v>16.59852274968637</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.6435798228513215</v>
+        <v>0.5643646102535416</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0538887891332323</v>
+        <v>-0.032086691778714</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1436</v>
+        <v>1338</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>193.9889519511302</v>
+        <v>194.1956074803861</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>35.7</v>
+        <v>15.45</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>22.80126562420216</v>
+        <v>38.53294382245742</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>36.3003899844843</v>
+        <v>32.69560096168198</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.331807290328376</v>
+        <v>0.6435798228513215</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.4751631328456511</v>
+        <v>-0.0538887891332323</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1464</v>
+        <v>1436</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>193.2804913902989</v>
+        <v>193.9889519511302</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>10.3</v>
+        <v>35.7</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>44.55741250310064</v>
+        <v>22.80126562420216</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>11.43481811516411</v>
+        <v>36.3003899844843</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6707253114574483</v>
+        <v>0.331807290328376</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0316280058209525</v>
+        <v>-0.4751631328456511</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1582</v>
+        <v>1464</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>193.2500522476155</v>
+        <v>193.2804913902989</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>71</v>
+        <v>10.3</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>42.54341523195627</v>
+        <v>44.55741250310064</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>41.13430311773981</v>
+        <v>11.43481811516411</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.9187822358359224</v>
+        <v>0.6707253114574483</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.8559238089904397</v>
+        <v>-0.0316280058209525</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1103</v>
+        <v>1582</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>190.1736717740579</v>
+        <v>193.2500522476155</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>38.98342680891469</v>
+        <v>42.54341523195627</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>11.45365350503299</v>
+        <v>41.13430311773981</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.5047442963496581</v>
+        <v>0.9187822358359224</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0470384667429424</v>
+        <v>0.8559238089904397</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1304</v>
+        <v>1103</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>190.1084686787033</v>
+        <v>190.1736717740579</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>11.6</v>
+        <v>13</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>39.10995705356871</v>
+        <v>38.98342680891469</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>18.2531555860763</v>
+        <v>11.45365350503299</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.523463942425198</v>
+        <v>0.5047442963496581</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.167142275544293</v>
+        <v>-0.0470384667429424</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1109</v>
+        <v>1304</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>189.1301511861772</v>
+        <v>190.1084686787033</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>13.55</v>
+        <v>11.6</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>26.94532599260918</v>
+        <v>39.10995705356871</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>36.76041998631722</v>
+        <v>18.2531555860763</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.4010770399376076</v>
+        <v>0.523463942425198</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0173592088207749</v>
+        <v>-0.167142275544293</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1473</v>
+        <v>1109</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>182.7501677215899</v>
+        <v>189.1301511861772</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>19.8</v>
+        <v>13.55</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>41.79489441633846</v>
+        <v>26.94532599260918</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>11.64559966690169</v>
+        <v>36.76041998631722</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.6772951043506992</v>
+        <v>0.4010770399376076</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0267809026317509</v>
+        <v>-0.0173592088207749</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1323</v>
+        <v>1473</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>179.8662778583362</v>
+        <v>182.7501677215899</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>19.75</v>
+        <v>19.8</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>45.0736987661716</v>
+        <v>41.79489441633846</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>13.03684626021491</v>
+        <v>11.64559966690169</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.3624365797221673</v>
+        <v>0.6772951043506992</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0268417045748778</v>
+        <v>-0.0267809026317509</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1441</v>
+        <v>1323</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>177.0273600094997</v>
+        <v>179.8662778583362</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>19.75</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>40.22165358023432</v>
+        <v>45.0736987661716</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>13.7177620302524</v>
+        <v>13.03684626021491</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.8925928580765128</v>
+        <v>0.3624365797221673</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0104465096721849</v>
+        <v>-0.0268417045748778</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1521</v>
+        <v>1441</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>176.2101940414049</v>
+        <v>177.0273600094997</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>25</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>42.64231247660154</v>
+        <v>40.22165358023432</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>12.01765564012601</v>
+        <v>13.7177620302524</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.322590094127214</v>
+        <v>0.8925928580765128</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0088279247501742</v>
+        <v>-0.0104465096721849</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1452</v>
+        <v>1521</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>174.1885886009908</v>
+        <v>176.2101940414049</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>11.15</v>
+        <v>25</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>41.90450015819064</v>
+        <v>42.64231247660154</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>19.19777242735914</v>
+        <v>12.01765564012601</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.075820585923126</v>
+        <v>1.322590094127214</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0729977951785882</v>
+        <v>-0.0088279247501742</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1324</v>
+        <v>1452</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>172.9776602820235</v>
+        <v>174.1885886009908</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>11.15</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>34.67512205731607</v>
+        <v>41.90450015819064</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>21.28974878031184</v>
+        <v>19.19777242735914</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.3536973362013537</v>
+        <v>1.075820585923126</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0318441575323458</v>
+        <v>-0.0729977951785882</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1108</v>
+        <v>1324</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>166.4746081109591</v>
+        <v>172.9776602820235</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>11.95</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>28.08155004531913</v>
+        <v>34.67512205731607</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>54.02279564379615</v>
+        <v>21.28974878031184</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.2209568949297648</v>
+        <v>0.3536973362013537</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0009642087158037999</v>
+        <v>-0.0318441575323458</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1454</v>
+        <v>1108</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>166.3705632127774</v>
+        <v>166.4746081109591</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>12.95</v>
+        <v>11.95</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>53.2749205966608</v>
+        <v>28.08155004531913</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>12.23446621805793</v>
+        <v>54.02279564379615</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.1062396001843286</v>
+        <v>0.2209568949297648</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0399353363143798</v>
+        <v>-0.0009642087158037999</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1310</v>
+        <v>1454</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>166.3561227282204</v>
+        <v>166.3705632127774</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>8.17</v>
+        <v>12.95</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>41.01733964705819</v>
+        <v>53.2749205966608</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>28.47764478670654</v>
+        <v>12.23446621805793</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.9824072224329627</v>
+        <v>0.1062396001843286</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.2509639121974926</v>
+        <v>0.0399353363143798</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1465</v>
+        <v>1310</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>159.2873165571187</v>
+        <v>166.3561227282204</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>12.45</v>
+        <v>8.17</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>44.71864724837144</v>
+        <v>41.01733964705819</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>15.62835636812409</v>
+        <v>28.47764478670654</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.416548485551512</v>
+        <v>0.9824072224329627</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0504918914035113</v>
+        <v>-0.2509639121974926</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1535</v>
+        <v>1465</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>158.4746321393723</v>
+        <v>159.2873165571187</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>45.7</v>
+        <v>12.45</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>33.8918195122415</v>
+        <v>44.71864724837144</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>22.85423359644382</v>
+        <v>15.62835636812409</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.4722975891418003</v>
+        <v>1.416548485551512</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.1037796763017238</v>
+        <v>-0.0504918914035113</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1445</v>
+        <v>1535</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>157.0700535638681</v>
+        <v>158.4746321393723</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>10.45</v>
+        <v>45.7</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>37.79614510232823</v>
+        <v>33.8918195122415</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>16.25213684263496</v>
+        <v>22.85423359644382</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.84570719843684</v>
+        <v>0.4722975891418003</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0440160099679165</v>
+        <v>-0.1037796763017238</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1340</v>
+        <v>1445</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>154.1344388542196</v>
+        <v>157.0700535638681</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>5.06</v>
+        <v>10.45</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>37.49320670369593</v>
+        <v>37.79614510232823</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>14.1381712392156</v>
+        <v>16.25213684263496</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.4502409360755584</v>
+        <v>1.84570719843684</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0129221492618855</v>
+        <v>-0.0440160099679165</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1201</v>
+        <v>1340</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>153.8028908340358</v>
+        <v>154.1344388542196</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>12.05</v>
+        <v>5.06</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>37.76660605700096</v>
+        <v>37.49320670369593</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>14.61770201897394</v>
+        <v>14.1381712392156</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.6304846179501576</v>
+        <v>0.4502409360755584</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.050868666204699</v>
+        <v>-0.0129221492618855</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1410</v>
+        <v>1201</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>152.4492312898823</v>
+        <v>153.8028908340358</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>25.9</v>
+        <v>12.05</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>49.48195940077935</v>
+        <v>37.76660605700096</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>17.52070928359448</v>
+        <v>14.61770201897394</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.595769059944538</v>
+        <v>0.6304846179501576</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0604751245455402</v>
+        <v>-0.050868666204699</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>1539</v>
+        <v>1410</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>巨庭</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>144.7101248505348</v>
+        <v>152.4492312898823</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>16.1</v>
+        <v>25.9</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>51.5594536824678</v>
+        <v>49.48195940077935</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>18.56376663978413</v>
+        <v>17.52070928359448</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.4721481070683731</v>
+        <v>0.595769059944538</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.0046956571329592</v>
+        <v>-0.0604751245455402</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1305</v>
+        <v>1539</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>巨庭</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>140.757936196441</v>
+        <v>144.7101248505348</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>11.35</v>
+        <v>16.1</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>39.47711379409027</v>
+        <v>51.5594536824678</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>20.9398131597514</v>
+        <v>18.56376663978413</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.3743160243668549</v>
+        <v>0.4721481070683731</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.1095188107708554</v>
+        <v>-0.0046956571329592</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1440</v>
+        <v>1305</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>139.8842470516022</v>
+        <v>140.757936196441</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>12.3</v>
+        <v>11.35</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>37.77405766214889</v>
+        <v>39.47711379409027</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>20.19409779915525</v>
+        <v>20.9398131597514</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.3513535116661764</v>
+        <v>0.3743160243668549</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.0698616446651121</v>
+        <v>-0.1095188107708554</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1308</v>
+        <v>1440</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>134.858412548295</v>
+        <v>139.8842470516022</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>13</v>
+        <v>12.3</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>41.17739338963673</v>
+        <v>37.77405766214889</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>18.09667748049057</v>
+        <v>20.19409779915525</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.4560152985201569</v>
+        <v>0.3513535116661764</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.1552977697831166</v>
+        <v>-0.0698616446651121</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1316</v>
+        <v>1308</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>131.3265602016055</v>
+        <v>134.858412548295</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>13</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>43.87017013954897</v>
+        <v>41.17739338963673</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>18.72597387665619</v>
+        <v>18.09667748049057</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.8895989454637975</v>
+        <v>0.4560152985201569</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.001569943183187</v>
+        <v>-0.1552977697831166</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1104</v>
+        <v>1316</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>126.3048070485362</v>
+        <v>131.3265602016055</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>26.4</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>39.73599536816389</v>
+        <v>43.87017013954897</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>19.00460860451599</v>
+        <v>18.72597387665619</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.8471604277258886</v>
+        <v>0.8895989454637975</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.0251406138367212</v>
+        <v>-0.001569943183187</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>1453</v>
+        <v>1104</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>121.2964735495063</v>
+        <v>126.3048070485362</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>11.15</v>
+        <v>26.4</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>46.92150680824388</v>
+        <v>39.73599536816389</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>12.47678164595172</v>
+        <v>19.00460860451599</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.9500057552852704</v>
+        <v>0.8471604277258886</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.0127681158705213</v>
+        <v>0.0251406138367212</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>120.100301833193</v>
+        <v>121.2964735495063</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>8.85</v>
+        <v>11.15</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>43.59974981499847</v>
+        <v>46.92150680824388</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>18.64577338518697</v>
+        <v>12.47678164595172</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.4330638613217914</v>
+        <v>0.9500057552852704</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0410010893932501</v>
+        <v>0.0127681158705213</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>109.3804809391478</v>
+        <v>120.100301833193</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>14.25</v>
+        <v>8.85</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>46.9346175346271</v>
+        <v>43.59974981499847</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>10.84913168015882</v>
+        <v>18.64577338518697</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.7275648568159503</v>
+        <v>0.4330638613217914</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.0015252153705577</v>
+        <v>-0.0410010893932501</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>1540</v>
+        <v>1457</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>89.37426167163886</v>
+        <v>109.3804809391478</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>20.35</v>
+        <v>14.25</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>43.014969197618</v>
+        <v>46.9346175346271</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>20.78971600650826</v>
+        <v>10.84913168015882</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.763778240455955</v>
+        <v>0.7275648568159503</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.1578758267107037</v>
+        <v>0.0015252153705577</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>1512</v>
+        <v>1540</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>喬福</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>67.517031928682</v>
+        <v>89.37426167163886</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>6.64</v>
+        <v>20.35</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>42.17241569504521</v>
+        <v>43.014969197618</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>9.666433259731342</v>
+        <v>20.78971600650826</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>1.303807915583314</v>
+        <v>0.763778240455955</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-0.006329141741175</v>
+        <v>-0.1578758267107037</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>1541</v>
+        <v>1512</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>66.65178744771221</v>
+        <v>67.517031928682</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>21.5</v>
+        <v>6.64</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,13 +7389,13 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>48.34243392620471</v>
+        <v>42.17241569504521</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>13.27446495698364</v>
+        <v>9.666433259731342</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.9183807656747248</v>
+        <v>1.303807915583314</v>
       </c>
       <c r="K131" s="2" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.0115660451173739</v>
+        <v>-0.006329141741175</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7417,52 +7417,105 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
+        <v>1541</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>錩泰</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>66.65178744771221</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>48.34243392620471</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>13.27446495698364</v>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>0.9183807656747248</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N132" s="2" t="n">
+        <v>-0.0115660451173739</v>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
         <v>1417</v>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>嘉裕</t>
         </is>
       </c>
-      <c r="C132" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D132" s="2" t="n">
+      <c r="C133" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D133" s="2" t="n">
         <v>61.08722613440533</v>
       </c>
-      <c r="E132" s="2" t="n">
+      <c r="E133" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H132" s="2" t="n">
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H133" s="2" t="n">
         <v>41.20765749480406</v>
       </c>
-      <c r="I132" s="2" t="n">
+      <c r="I133" s="2" t="n">
         <v>18.49062543113661</v>
       </c>
-      <c r="J132" s="2" t="n">
+      <c r="J133" s="2" t="n">
         <v>0.5469193334414678</v>
       </c>
-      <c r="K132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M132" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N132" s="2" t="n">
+      <c r="K133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N133" s="2" t="n">
         <v>-0.0434337609537484</v>
       </c>
-      <c r="O132" s="2" t="inlineStr">
+      <c r="O133" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
